--- a/data/trans_dic/P39A3_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P39A3_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 93,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>89,29; 94,26</t>
+          <t>89,59; 94,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,05; 94,03</t>
+          <t>90,08; 94,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,56; 93,76</t>
+          <t>90,54; 93,58</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,65; 95,07</t>
+          <t>90,54; 94,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,39; 91,87</t>
+          <t>86,18; 91,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,45; 92,96</t>
+          <t>89,5; 93,14</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,63; 97,94</t>
+          <t>89,58; 97,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,06; 92,18</t>
+          <t>84,54; 92,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,33; 97,16</t>
+          <t>89,27; 97,3</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,85; 94,3</t>
+          <t>90,87; 94,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90,38; 96,33</t>
+          <t>90,44; 96,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,37; 94,91</t>
+          <t>91,33; 95,16</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,41; 92,26</t>
+          <t>85,97; 92,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,51; 90,93</t>
+          <t>60,92; 90,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65,37; 90,49</t>
+          <t>68,0; 90,55</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78,01; 93,94</t>
+          <t>76,93; 93,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,75; 93,63</t>
+          <t>89,85; 93,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88,05; 92,75</t>
+          <t>88,41; 92,84</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>90,83; 94,04</t>
+          <t>90,98; 94,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,55; 91,89</t>
+          <t>82,78; 91,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,27; 92,23</t>
+          <t>87,51; 92,32</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 93,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>440084; 464605</t>
+          <t>441597; 464315</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>394816; 412266</t>
+          <t>394949; 412230</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>843393; 873257</t>
+          <t>843230; 871512</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>401930; 421551</t>
+          <t>401457; 420783</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>320862; 341191</t>
+          <t>320086; 340667</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>728868; 757466</t>
+          <t>729254; 758944</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>581813; 635801</t>
+          <t>581509; 635944</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>135830; 147206</t>
+          <t>135001; 147792</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>722530; 785897</t>
+          <t>722025; 787038</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>887070; 920723</t>
+          <t>887236; 919325</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>857290; 913739</t>
+          <t>857838; 916600</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1758876; 1826869</t>
+          <t>1757966; 1831715</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>360325; 384745</t>
+          <t>358508; 385022</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>419106; 674388</t>
+          <t>451806; 674081</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>757427; 1048538</t>
+          <t>787854; 1049139</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>160362; 193123</t>
+          <t>158157; 192412</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>604589; 630683</t>
+          <t>605220; 629434</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>774142; 815466</t>
+          <t>777252; 816201</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2892436; 2994625</t>
+          <t>2897282; 2996102</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2751657; 3063129</t>
+          <t>2759443; 3066048</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5688290; 6011047</t>
+          <t>5703458; 6017393</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A3_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P39A3_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>89,59; 94,2</t>
+          <t>89,8; 94,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,08; 94,02</t>
+          <t>89,61; 93,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,54; 93,58</t>
+          <t>90,36; 93,6</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,54; 94,9</t>
+          <t>89,65; 94,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,18; 91,73</t>
+          <t>86,48; 91,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,5; 93,14</t>
+          <t>89,28; 92,68</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,58; 97,97</t>
+          <t>87,15; 92,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,54; 92,55</t>
+          <t>84,28; 92,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,27; 97,3</t>
+          <t>87,22; 91,75</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,87; 94,16</t>
+          <t>90,15; 93,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90,44; 96,63</t>
+          <t>88,9; 92,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,33; 95,16</t>
+          <t>90,13; 92,58</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>85,97; 92,33</t>
+          <t>84,68; 91,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60,92; 90,89</t>
+          <t>88,01; 91,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68,0; 90,55</t>
+          <t>87,45; 90,77</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76,93; 93,6</t>
+          <t>80,44; 94,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,85; 93,44</t>
+          <t>89,99; 93,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88,41; 92,84</t>
+          <t>88,84; 92,89</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>90,98; 94,09</t>
+          <t>89,92; 92,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,78; 91,98</t>
+          <t>89,81; 91,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,51; 92,32</t>
+          <t>90,16; 91,5</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>454397</t>
+          <t>495908</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>404494</t>
+          <t>438362</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>858891</t>
+          <t>934271</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>441597; 464315</t>
+          <t>481995; 507092</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>394949; 412230</t>
+          <t>428163; 446958</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>843230; 871512</t>
+          <t>916764; 949593</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>412729</t>
+          <t>438516</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>331718</t>
+          <t>365259</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>744447</t>
+          <t>803775</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>401457; 420783</t>
+          <t>424998; 447447</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>320086; 340667</t>
+          <t>353754; 376123</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>729254; 758944</t>
+          <t>788456; 818504</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>611054</t>
+          <t>402704</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>142174</t>
+          <t>158632</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>753230</t>
+          <t>561335</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>581509; 635944</t>
+          <t>388815; 413666</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>135001; 147792</t>
+          <t>150998; 164971</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>722025; 787038</t>
+          <t>545421; 573724</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>904485</t>
+          <t>979536</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>881117</t>
+          <t>748797</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1785601</t>
+          <t>1728334</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>887236; 919325</t>
+          <t>960370; 997204</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>857838; 916600</t>
+          <t>734214; 761195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1757966; 1831715</t>
+          <t>1704472; 1750886</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>373210</t>
+          <t>421072</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>607407</t>
+          <t>673565</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>980617</t>
+          <t>1094637</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>358508; 385022</t>
+          <t>404018; 434148</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>451806; 674081</t>
+          <t>660130; 685826</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>787854; 1049139</t>
+          <t>1073175; 1113942</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>180542</t>
+          <t>175286</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>618213</t>
+          <t>682341</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>798755</t>
+          <t>857626</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>158157; 192412</t>
+          <t>158983; 185807</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>605220; 629434</t>
+          <t>668952; 695225</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>777252; 816201</t>
+          <t>835973; 874140</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2936417</t>
+          <t>2913024</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2985124</t>
+          <t>3066956</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5921541</t>
+          <t>5979980</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2897282; 2996102</t>
+          <t>2874837; 2945340</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2759443; 3066048</t>
+          <t>3040300; 3096217</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5703458; 6017393</t>
+          <t>5934916; 6022618</t>
         </is>
       </c>
     </row>
